--- a/ONCHO/Entomological survey Survey/Nigeria/2025/ng_oncho_2503_5_hlc_tar.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2025/ng_oncho_2503_5_hlc_tar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A1BDF3-AC40-4BEC-A0BF-D7A8E85588F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454C1675-DCBE-4A75-B44A-3884743510FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="246">
   <si>
     <t>type</t>
   </si>
@@ -548,9 +548,6 @@
     <t>ng_oncho_2503_5_hlc_tar</t>
   </si>
   <si>
-    <t>(Taraba) 5. Human Landing Catches</t>
-  </si>
-  <si>
     <t>TAR_BAL_N_054</t>
   </si>
   <si>
@@ -558,6 +555,222 @@
   </si>
   <si>
     <t>TAR_SAR_N_053</t>
+  </si>
+  <si>
+    <t>(Taraba) 5. Human Landing Catches V4</t>
+  </si>
+  <si>
+    <t>ARDOKOLA</t>
+  </si>
+  <si>
+    <t>BALI</t>
+  </si>
+  <si>
+    <t>DONGA</t>
+  </si>
+  <si>
+    <t>GASHAKA</t>
+  </si>
+  <si>
+    <t>GASSOL</t>
+  </si>
+  <si>
+    <t>IBI</t>
+  </si>
+  <si>
+    <t>KARIM LAMIDO</t>
+  </si>
+  <si>
+    <t>KURMI</t>
+  </si>
+  <si>
+    <t>LAU</t>
+  </si>
+  <si>
+    <t>SARDAUNA</t>
+  </si>
+  <si>
+    <t>TAKUM</t>
+  </si>
+  <si>
+    <t>USSA</t>
+  </si>
+  <si>
+    <t>WUKARI</t>
+  </si>
+  <si>
+    <t>YORRO</t>
+  </si>
+  <si>
+    <t>SIBRE</t>
+  </si>
+  <si>
+    <t>ZANGO KOBI</t>
+  </si>
+  <si>
+    <t>DAKKA</t>
+  </si>
+  <si>
+    <t>GAZABU</t>
+  </si>
+  <si>
+    <t>KURMIN GORO</t>
+  </si>
+  <si>
+    <t>MAIHULA</t>
+  </si>
+  <si>
+    <t>MAYO KAM</t>
+  </si>
+  <si>
+    <t>PAMANGA</t>
+  </si>
+  <si>
+    <t>BIBINU</t>
+  </si>
+  <si>
+    <t>SANSO(ANANUM)</t>
+  </si>
+  <si>
+    <t>SUNTAI DONGA</t>
+  </si>
+  <si>
+    <t>TISA</t>
+  </si>
+  <si>
+    <t>BODEL</t>
+  </si>
+  <si>
+    <t>FILINGA</t>
+  </si>
+  <si>
+    <t>GANGWEREN/GANGUMI</t>
+  </si>
+  <si>
+    <t>GARBABI</t>
+  </si>
+  <si>
+    <t>GARIN YUSUF</t>
+  </si>
+  <si>
+    <t>JAURO JALLO</t>
+  </si>
+  <si>
+    <t>MAI IDANU</t>
+  </si>
+  <si>
+    <t>NYABAR</t>
+  </si>
+  <si>
+    <t>SERTI</t>
+  </si>
+  <si>
+    <t>GARIN KUKA</t>
+  </si>
+  <si>
+    <t>NAMNAI</t>
+  </si>
+  <si>
+    <t>SENDIRDE</t>
+  </si>
+  <si>
+    <t>DAMPAR</t>
+  </si>
+  <si>
+    <t>IBI RIMI UKU I (ANGWAN GALADIMA)</t>
+  </si>
+  <si>
+    <t>K/WANZA</t>
+  </si>
+  <si>
+    <t>KURMA (IYAKA)</t>
+  </si>
+  <si>
+    <t>MALA</t>
+  </si>
+  <si>
+    <t>TAPGAR</t>
+  </si>
+  <si>
+    <t>BAMBUKA</t>
+  </si>
+  <si>
+    <t>G/DUTSE (NWABILA)</t>
+  </si>
+  <si>
+    <t>GWOMU</t>
+  </si>
+  <si>
+    <t>JEN ARDIDO/JAKAN</t>
+  </si>
+  <si>
+    <t>KODEI</t>
+  </si>
+  <si>
+    <t>KUKA WAZIRI</t>
+  </si>
+  <si>
+    <t>WANZAMIN GOMU</t>
+  </si>
+  <si>
+    <t>WONG</t>
+  </si>
+  <si>
+    <t>BENTE SAMA</t>
+  </si>
+  <si>
+    <t>SHUWAKA</t>
+  </si>
+  <si>
+    <t>KATIBU</t>
+  </si>
+  <si>
+    <t>ANTERE</t>
+  </si>
+  <si>
+    <t>GONO</t>
+  </si>
+  <si>
+    <t>KABRI</t>
+  </si>
+  <si>
+    <t>MAYO-NDAGA</t>
+  </si>
+  <si>
+    <t>MBASO</t>
+  </si>
+  <si>
+    <t>NDUMYAJI</t>
+  </si>
+  <si>
+    <t>NGUBIN</t>
+  </si>
+  <si>
+    <t>CHENCHENJI</t>
+  </si>
+  <si>
+    <t>GALUMJE</t>
+  </si>
+  <si>
+    <t>FIKYU</t>
+  </si>
+  <si>
+    <t>KWESATI</t>
+  </si>
+  <si>
+    <t>LUMBU</t>
+  </si>
+  <si>
+    <t>BANTAJE</t>
+  </si>
+  <si>
+    <t>FIYAYI/ARUFU</t>
+  </si>
+  <si>
+    <t>RITI</t>
+  </si>
+  <si>
+    <t>DANDIKULU</t>
   </si>
 </sst>
 </file>
@@ -845,7 +1058,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1952,1193 +2175,1839 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="20"/>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="D28" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="D29" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D29" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D30" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="D31" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D31" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="D32" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="D32" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:5">
       <c r="A33" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:5">
       <c r="A34" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>120</v>
+        <v>181</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:5">
       <c r="A35" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="D35" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:5">
       <c r="A36" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="D36" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="D36" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:5">
       <c r="A37" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D37" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:5">
       <c r="A38" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:5">
       <c r="A39" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="D39" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D39" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:5">
       <c r="A40" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:5">
       <c r="A41" s="20" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D41" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="D41" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="20" t="s">
-        <v>83</v>
+    <row r="42" spans="1:5">
+      <c r="A42" s="20"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>47</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="20" t="s">
-        <v>83</v>
+        <v>189</v>
+      </c>
+      <c r="E43" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>47</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="20" t="s">
-        <v>83</v>
+        <v>190</v>
+      </c>
+      <c r="E44" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>47</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="20" t="s">
-        <v>83</v>
+        <v>191</v>
+      </c>
+      <c r="E45" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>47</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="20" t="s">
-        <v>83</v>
+        <v>192</v>
+      </c>
+      <c r="E46" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>47</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="20" t="s">
-        <v>83</v>
+        <v>193</v>
+      </c>
+      <c r="E47" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>47</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="20" t="s">
-        <v>83</v>
+        <v>194</v>
+      </c>
+      <c r="E48" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>47</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D49" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="20" t="s">
-        <v>83</v>
+        <v>195</v>
+      </c>
+      <c r="E49" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>47</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="D50" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="20" t="s">
-        <v>83</v>
+        <v>196</v>
+      </c>
+      <c r="E50" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>47</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="D51" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="20" t="s">
-        <v>83</v>
+        <v>197</v>
+      </c>
+      <c r="E51" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>47</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="20" t="s">
-        <v>83</v>
+        <v>198</v>
+      </c>
+      <c r="E52" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>47</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="20" t="s">
-        <v>83</v>
+        <v>199</v>
+      </c>
+      <c r="E53" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>47</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="20" t="s">
-        <v>83</v>
+        <v>200</v>
+      </c>
+      <c r="E54" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>47</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="20" t="s">
-        <v>83</v>
+        <v>201</v>
+      </c>
+      <c r="E55" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>47</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="20" t="s">
-        <v>83</v>
+        <v>202</v>
+      </c>
+      <c r="E56" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="31.5">
+      <c r="A57" t="s">
+        <v>47</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>138</v>
+        <v>203</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D57" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="20" t="s">
-        <v>83</v>
+        <v>203</v>
+      </c>
+      <c r="E57" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>47</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="20" t="s">
-        <v>83</v>
+        <v>204</v>
+      </c>
+      <c r="E58" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>47</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="20" t="s">
-        <v>83</v>
+        <v>205</v>
+      </c>
+      <c r="E59" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>47</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>116</v>
+        <v>206</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="D60" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="20" t="s">
-        <v>83</v>
+        <v>206</v>
+      </c>
+      <c r="E60" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>47</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="D61" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="20" t="s">
-        <v>83</v>
+        <v>207</v>
+      </c>
+      <c r="E61" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>47</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="20" t="s">
-        <v>83</v>
+        <v>208</v>
+      </c>
+      <c r="E62" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>47</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>122</v>
+        <v>209</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="20" t="s">
-        <v>83</v>
+        <v>209</v>
+      </c>
+      <c r="E63" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>47</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="20" t="s">
-        <v>83</v>
+        <v>210</v>
+      </c>
+      <c r="E64" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>47</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="20" t="s">
-        <v>83</v>
+        <v>179</v>
+      </c>
+      <c r="E65" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>47</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>147</v>
+        <v>211</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="20" t="s">
-        <v>83</v>
+        <v>211</v>
+      </c>
+      <c r="E66" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>47</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>128</v>
+        <v>212</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="20" t="s">
-        <v>83</v>
+        <v>212</v>
+      </c>
+      <c r="E67" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>47</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="20" t="s">
-        <v>83</v>
+        <v>213</v>
+      </c>
+      <c r="E68" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="31.5">
+      <c r="A69" t="s">
+        <v>47</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>125</v>
+        <v>214</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="20" t="s">
-        <v>83</v>
+        <v>214</v>
+      </c>
+      <c r="E69" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>47</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D70" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="20" t="s">
-        <v>83</v>
+        <v>215</v>
+      </c>
+      <c r="E70" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>47</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>119</v>
+        <v>216</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="20" t="s">
-        <v>83</v>
+        <v>216</v>
+      </c>
+      <c r="E71" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>47</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>118</v>
+        <v>217</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="20" t="s">
-        <v>83</v>
+        <v>217</v>
+      </c>
+      <c r="E72" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>47</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>152</v>
+        <v>218</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="D73" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="20" t="s">
-        <v>83</v>
+        <v>218</v>
+      </c>
+      <c r="E73" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>47</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>115</v>
+        <v>219</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="20" t="s">
-        <v>83</v>
+        <v>219</v>
+      </c>
+      <c r="E74" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>47</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>131</v>
+        <v>220</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="20" t="s">
-        <v>83</v>
+        <v>220</v>
+      </c>
+      <c r="E75" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>47</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>149</v>
+        <v>221</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="20" t="s">
-        <v>83</v>
+        <v>221</v>
+      </c>
+      <c r="E76" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>47</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>117</v>
+        <v>222</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="D77" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="20" t="s">
-        <v>83</v>
+        <v>222</v>
+      </c>
+      <c r="E77" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>47</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="D78" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="20" t="s">
-        <v>83</v>
+        <v>223</v>
+      </c>
+      <c r="E78" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>47</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="D79" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="20" t="s">
-        <v>83</v>
+        <v>224</v>
+      </c>
+      <c r="E79" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>47</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="D80" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="20" t="s">
-        <v>83</v>
+        <v>225</v>
+      </c>
+      <c r="E80" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>47</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="D81" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="20" t="s">
-        <v>83</v>
+        <v>226</v>
+      </c>
+      <c r="E81" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>47</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="D82" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="20" t="s">
-        <v>83</v>
+        <v>227</v>
+      </c>
+      <c r="E82" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>47</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>173</v>
+        <v>228</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="D83" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="20" t="s">
-        <v>83</v>
+        <v>228</v>
+      </c>
+      <c r="E83" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>47</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>145</v>
+        <v>229</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="D84" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="20" t="s">
-        <v>83</v>
+        <v>229</v>
+      </c>
+      <c r="E84" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>47</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>174</v>
+        <v>230</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="D85" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="20"/>
-      <c r="B86" s="19"/>
-      <c r="C86" s="19"/>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="20"/>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="20"/>
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="20"/>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="20"/>
-      <c r="B90" s="19"/>
-      <c r="C90" s="19"/>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="20"/>
-      <c r="B91" s="19"/>
-      <c r="C91" s="19"/>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="20"/>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="20"/>
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="20"/>
-      <c r="B94" s="19"/>
-      <c r="C94" s="19"/>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="20"/>
-      <c r="B95" s="19"/>
-      <c r="C95" s="19"/>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="20"/>
-      <c r="B96" s="19"/>
-      <c r="C96" s="19"/>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="20"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="20"/>
-      <c r="B98" s="19"/>
-      <c r="C98" s="19"/>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="20"/>
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="20"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="20"/>
+        <v>230</v>
+      </c>
+      <c r="E85" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>47</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="E86" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>47</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="E87" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>47</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="E88" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>47</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E89" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>47</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E90" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>47</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="E91" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>47</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="E92" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>47</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E93" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>47</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="C94" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E94" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>47</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="E95" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>47</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="C96" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="E96" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>47</v>
+      </c>
+      <c r="B97" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="E97" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>47</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="E98" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>47</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="E99" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>47</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="C100" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="E100" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="B101" s="19"/>
       <c r="C101" s="19"/>
     </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="20"/>
-      <c r="B102" s="19"/>
-      <c r="C102" s="19"/>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="20"/>
-      <c r="B103" s="19"/>
-      <c r="C103" s="19"/>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="20"/>
-      <c r="B104" s="19"/>
-      <c r="C104" s="19"/>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="20"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="19"/>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="20"/>
-      <c r="B106" s="19"/>
-      <c r="C106" s="19"/>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="20"/>
-      <c r="B107" s="19"/>
-      <c r="C107" s="19"/>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="20"/>
-      <c r="B108" s="19"/>
-      <c r="C108" s="19"/>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="20"/>
-      <c r="B109" s="19"/>
-      <c r="C109" s="19"/>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="20"/>
-      <c r="B110" s="19"/>
-      <c r="C110" s="19"/>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="20"/>
-      <c r="B111" s="19"/>
-      <c r="C111" s="19"/>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="20"/>
-      <c r="B112" s="19"/>
-      <c r="C112" s="19"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="20"/>
-      <c r="B113" s="19"/>
-      <c r="C113" s="19"/>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="20"/>
-      <c r="B114" s="19"/>
-      <c r="C114" s="19"/>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="20"/>
-      <c r="B115" s="19"/>
-      <c r="C115" s="19"/>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="20"/>
-      <c r="B116" s="19"/>
-      <c r="C116" s="19"/>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="20"/>
-      <c r="B117" s="19"/>
-      <c r="C117" s="19"/>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="20"/>
-      <c r="B118" s="19"/>
-      <c r="C118" s="19"/>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="20"/>
-      <c r="B119" s="19"/>
-      <c r="C119" s="19"/>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="20"/>
-      <c r="B120" s="19"/>
-      <c r="C120" s="19"/>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="20"/>
-      <c r="B121" s="19"/>
-      <c r="C121" s="19"/>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="20"/>
-      <c r="B122" s="19"/>
-      <c r="C122" s="19"/>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="20"/>
-      <c r="B123" s="19"/>
-      <c r="C123" s="19"/>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="20"/>
-      <c r="B124" s="19"/>
-      <c r="C124" s="19"/>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="20"/>
-      <c r="B125" s="19"/>
-      <c r="C125" s="19"/>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="20"/>
-      <c r="B126" s="19"/>
-      <c r="C126" s="19"/>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="20"/>
-      <c r="B127" s="19"/>
-      <c r="C127" s="19"/>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="20"/>
-      <c r="B128" s="19"/>
-      <c r="C128" s="19"/>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="20"/>
-      <c r="B129" s="19"/>
-      <c r="C129" s="19"/>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="20"/>
-      <c r="B130" s="19"/>
-      <c r="C130" s="19"/>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="20"/>
-      <c r="B131" s="19"/>
-      <c r="C131" s="19"/>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="20"/>
-      <c r="B132" s="19"/>
-      <c r="C132" s="19"/>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" s="20"/>
-      <c r="B133" s="19"/>
-      <c r="C133" s="19"/>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134" s="20"/>
-      <c r="B134" s="19"/>
-      <c r="C134" s="19"/>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135" s="20"/>
-      <c r="B135" s="19"/>
-      <c r="C135" s="19"/>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136" s="20"/>
-      <c r="B136" s="19"/>
-      <c r="C136" s="19"/>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" s="20"/>
-      <c r="B137" s="19"/>
-      <c r="C137" s="19"/>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" s="20"/>
-      <c r="B138" s="19"/>
-      <c r="C138" s="19"/>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" s="20"/>
-      <c r="B139" s="19"/>
-      <c r="C139" s="19"/>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" s="20"/>
-      <c r="B140" s="19"/>
-      <c r="C140" s="19"/>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" s="20"/>
-      <c r="B141" s="19"/>
-      <c r="C141" s="19"/>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142" s="20"/>
-      <c r="B142" s="19"/>
-      <c r="C142" s="19"/>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="A143" s="20"/>
-      <c r="B143" s="19"/>
-      <c r="C143" s="19"/>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" s="20"/>
-      <c r="B144" s="19"/>
-      <c r="C144" s="19"/>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" s="20"/>
-      <c r="B145" s="19"/>
-      <c r="C145" s="19"/>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" s="20"/>
-      <c r="B146" s="19"/>
-      <c r="C146" s="19"/>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147" s="20"/>
-      <c r="B147" s="19"/>
-      <c r="C147" s="19"/>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148" s="20"/>
-      <c r="B148" s="19"/>
-      <c r="C148" s="19"/>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149" s="20"/>
-      <c r="B149" s="19"/>
-      <c r="C149" s="19"/>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" s="20"/>
-      <c r="B150" s="19"/>
-      <c r="C150" s="19"/>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" s="20"/>
-      <c r="B151" s="19"/>
-      <c r="C151" s="19"/>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" s="20"/>
-      <c r="B152" s="19"/>
-      <c r="C152" s="19"/>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" s="20"/>
-      <c r="B153" s="19"/>
-      <c r="C153" s="19"/>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" s="20"/>
-      <c r="B154" s="19"/>
-      <c r="C154" s="19"/>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155" s="20"/>
-      <c r="B155" s="19"/>
-      <c r="C155" s="19"/>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156" s="20"/>
-      <c r="B156" s="19"/>
-      <c r="C156" s="19"/>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" s="20"/>
-      <c r="B157" s="19"/>
-      <c r="C157" s="19"/>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" s="20"/>
-      <c r="B158" s="19"/>
-      <c r="C158" s="19"/>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" s="20"/>
-      <c r="B159" s="19"/>
-      <c r="C159" s="19"/>
-    </row>
-    <row r="160" spans="1:3">
+    <row r="102" spans="1:6">
+      <c r="A102" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C102" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F102" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F103" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F104" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F105" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F106" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F107" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F108" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F109" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C110" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F110" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C111" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="F111" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C112" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F112" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F113" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F114" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="F115" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="F116" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F117" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F118" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F119" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C120" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F120" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F121" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C122" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="F122" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="F123" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="F124" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="F125" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F126" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F127" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C128" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F128" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C129" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F129" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C130" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="F130" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C131" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F131" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C132" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F132" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F133" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B134" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C134" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F134" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C135" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F135" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C136" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="F136" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B137" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C137" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F137" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C138" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="F138" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F139" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C140" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F140" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F141" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="F142" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F143" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C144" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F144" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F145" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F146" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="F147" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C148" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F148" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="F149" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F150" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F151" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F152" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B153" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C153" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F153" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B154" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C154" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F154" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B155" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C155" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="F155" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B156" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C156" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="F156" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B157" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C157" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F157" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B158" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C158" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="F158" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B159" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C159" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F159" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" s="20"/>
       <c r="B160" s="19"/>
       <c r="C160" s="19"/>
@@ -6319,9 +7188,9 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C506:C551">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28:C74">
+  <conditionalFormatting sqref="C102:C148">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6351,7 +7220,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>170</v>
